--- a/fanta/Calendario_SarkiaLega-25-26.xlsx
+++ b/fanta/Calendario_SarkiaLega-25-26.xlsx
@@ -2723,16 +2723,16 @@
         <v>11</v>
       </c>
       <c r="B80" s="6">
-        <v>0</v>
+        <v>71.5</v>
       </c>
       <c r="C80" s="6">
-        <v>0</v>
+        <v>59.5</v>
       </c>
       <c r="D80" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E80" s="8" t="s">
-        <v>97</v>
+        <v>18</v>
       </c>
       <c r="G80" s="5" t="s">
         <v>6</v>
@@ -2755,16 +2755,16 @@
         <v>15</v>
       </c>
       <c r="B81" s="6">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="C81" s="6">
-        <v>0</v>
+        <v>72.5</v>
       </c>
       <c r="D81" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E81" s="8" t="s">
-        <v>97</v>
+        <v>13</v>
       </c>
       <c r="G81" s="5" t="s">
         <v>7</v>
@@ -2787,16 +2787,16 @@
         <v>9</v>
       </c>
       <c r="B82" s="6">
-        <v>0</v>
+        <v>63.5</v>
       </c>
       <c r="C82" s="6">
-        <v>0</v>
+        <v>63.5</v>
       </c>
       <c r="D82" s="7" t="s">
         <v>6</v>
       </c>
       <c r="E82" s="8" t="s">
-        <v>97</v>
+        <v>48</v>
       </c>
       <c r="G82" s="5" t="s">
         <v>14</v>
@@ -2819,16 +2819,16 @@
         <v>17</v>
       </c>
       <c r="B83" s="6">
-        <v>0</v>
+        <v>76.5</v>
       </c>
       <c r="C83" s="6">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="D83" s="7" t="s">
         <v>12</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>97</v>
+        <v>13</v>
       </c>
       <c r="G83" s="5" t="s">
         <v>12</v>

--- a/fanta/Calendario_SarkiaLega-25-26.xlsx
+++ b/fanta/Calendario_SarkiaLega-25-26.xlsx
@@ -2787,7 +2787,7 @@
         <v>9</v>
       </c>
       <c r="B82" s="6">
-        <v>63.5</v>
+        <v>64</v>
       </c>
       <c r="C82" s="6">
         <v>63.5</v>

--- a/fanta/Calendario_SarkiaLega-25-26.xlsx
+++ b/fanta/Calendario_SarkiaLega-25-26.xlsx
@@ -305,19 +305,19 @@
     <t>34ª Giornata serie a</t>
   </si>
   <si>
+    <t>33ª Giornata lega</t>
+  </si>
+  <si>
+    <t>35ª Giornata serie a</t>
+  </si>
+  <si>
+    <t>34ª Giornata lega</t>
+  </si>
+  <si>
+    <t>36ª Giornata serie a</t>
+  </si>
+  <si>
     <t>-</t>
-  </si>
-  <si>
-    <t>33ª Giornata lega</t>
-  </si>
-  <si>
-    <t>35ª Giornata serie a</t>
-  </si>
-  <si>
-    <t>34ª Giornata lega</t>
-  </si>
-  <si>
-    <t>36ª Giornata serie a</t>
   </si>
   <si>
     <t>35ª Giornata lega</t>
@@ -2738,16 +2738,16 @@
         <v>6</v>
       </c>
       <c r="H80" s="6">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I80" s="6">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="J80" s="7" t="s">
         <v>15</v>
       </c>
       <c r="K80" s="8" t="s">
-        <v>97</v>
+        <v>47</v>
       </c>
     </row>
     <row r="81">
@@ -2770,16 +2770,16 @@
         <v>7</v>
       </c>
       <c r="H81" s="6">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="I81" s="6">
-        <v>0</v>
+        <v>73.5</v>
       </c>
       <c r="J81" s="7" t="s">
         <v>11</v>
       </c>
       <c r="K81" s="8" t="s">
-        <v>97</v>
+        <v>16</v>
       </c>
     </row>
     <row r="82">
@@ -2802,16 +2802,16 @@
         <v>14</v>
       </c>
       <c r="H82" s="6">
-        <v>0</v>
+        <v>71.5</v>
       </c>
       <c r="I82" s="6">
-        <v>0</v>
+        <v>66.5</v>
       </c>
       <c r="J82" s="7" t="s">
         <v>17</v>
       </c>
       <c r="K82" s="8" t="s">
-        <v>97</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83">
@@ -2834,34 +2834,34 @@
         <v>12</v>
       </c>
       <c r="H83" s="6">
-        <v>0</v>
+        <v>65.5</v>
       </c>
       <c r="I83" s="6">
-        <v>0</v>
+        <v>70.5</v>
       </c>
       <c r="J83" s="7" t="s">
         <v>9</v>
       </c>
       <c r="K83" s="8" t="s">
-        <v>97</v>
+        <v>31</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B84" s="2"/>
       <c r="C84" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D84" s="3"/>
       <c r="E84" s="4"/>
       <c r="G84" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H84" s="2"/>
       <c r="I84" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J84" s="3"/>
       <c r="K84" s="4"/>
@@ -2880,7 +2880,7 @@
         <v>6</v>
       </c>
       <c r="E85" s="8" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G85" s="5" t="s">
         <v>6</v>
@@ -2895,7 +2895,7 @@
         <v>17</v>
       </c>
       <c r="K85" s="8" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="86">
@@ -2912,7 +2912,7 @@
         <v>9</v>
       </c>
       <c r="E86" s="8" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G86" s="5" t="s">
         <v>7</v>
@@ -2927,7 +2927,7 @@
         <v>14</v>
       </c>
       <c r="K86" s="8" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="87">
@@ -2944,7 +2944,7 @@
         <v>12</v>
       </c>
       <c r="E87" s="8" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G87" s="5" t="s">
         <v>15</v>
@@ -2959,7 +2959,7 @@
         <v>12</v>
       </c>
       <c r="K87" s="8" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="88">
@@ -2976,7 +2976,7 @@
         <v>7</v>
       </c>
       <c r="E88" s="8" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G88" s="5" t="s">
         <v>9</v>
@@ -2991,7 +2991,7 @@
         <v>11</v>
       </c>
       <c r="K88" s="8" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="89">
@@ -3019,7 +3019,7 @@
         <v>15</v>
       </c>
       <c r="E90" s="8" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="91">
@@ -3036,7 +3036,7 @@
         <v>6</v>
       </c>
       <c r="E91" s="8" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="92">
@@ -3053,7 +3053,7 @@
         <v>9</v>
       </c>
       <c r="E92" s="8" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="93">
@@ -3070,7 +3070,7 @@
         <v>7</v>
       </c>
       <c r="E93" s="8" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
